--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output5.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output5.xlsx
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>6.505166016334476e-05</v>
+        <v>0.0005599550529367897</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001805710042744937</v>
+        <v>0.0008870771030177027</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>6.505166016334476e-05</v>
+        <v>0.0005599550529367897</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001690190698633788</v>
+        <v>0.0008543648980096114</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>7.438872600615926e-05</v>
+        <v>0.0007505040559887258</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0001595560354776568</v>
+        <v>0.0008439788138075228</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.0002870467807226822</v>
+        <v>0.000378216583513647</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0001723051100021594</v>
+        <v>0.0007974025907781352</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001383363641005462</v>
+        <v>0.0001648098577340351</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001689082354119981</v>
+        <v>0.0007341433174737252</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001230372151865406</v>
+        <v>0.000402408521969925</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001643211333894523</v>
+        <v>0.0007009698379233451</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>4.909173106545919e-05</v>
+        <v>0.0004905272867109583</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000152798193157053</v>
+        <v>0.0006799255828021064</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>5.192366060218364e-05</v>
+        <v>0.0004919456689275297</v>
       </c>
       <c r="R9" t="n">
-        <v>0.000142710739901566</v>
+        <v>0.0006611275914146488</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001562438269942524</v>
+        <v>0.000626816282822863</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001440640486108347</v>
+        <v>0.0006576964605554702</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.0002397485289553745</v>
+        <v>0.0005700366779007263</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001536324966452887</v>
+        <v>0.0006489304822899957</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.0001206295682473102</v>
+        <v>0.0003623421596286699</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001503322038054908</v>
+        <v>0.0006202716500238631</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001081656383633927</v>
+        <v>0.0002882772303515796</v>
       </c>
       <c r="R13" t="n">
-        <v>0.000146115547261281</v>
+        <v>0.0005870722080566348</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>8.204391656168812e-05</v>
+        <v>0.000453850707320261</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0001397083841913217</v>
+        <v>0.0005737500579829974</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>8.204391656168812e-05</v>
+        <v>0.000453850707320261</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0001339419374283583</v>
+        <v>0.0005617601229167237</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>0.0003051173964709489</v>
+        <v>0.0007274783851394875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0001510594833326174</v>
+        <v>0.0005783319491390001</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0.0002589928784431973</v>
+        <v>0.0006699809713196849</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001618528228436754</v>
+        <v>0.0005874968513570686</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001831800554248671</v>
+        <v>0.0003700899334545618</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0001639855461017945</v>
+        <v>0.0005657561595668178</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>9.246253506595874e-05</v>
+        <v>0.0004658941322448205</v>
       </c>
       <c r="R19" t="n">
-        <v>0.000156833244998211</v>
+        <v>0.0005557699568346182</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>9.246253506595874e-05</v>
+        <v>0.0004658941322448205</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0001503961740049858</v>
+        <v>0.0005467823743756385</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>7.159564395177937e-05</v>
+        <v>0.0005395281946049808</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0001425161209996651</v>
+        <v>0.0005460569563985727</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>0.0001854842375260116</v>
+        <v>0.0007213093493986245</v>
       </c>
       <c r="R22" t="n">
-        <v>0.0001468129326522998</v>
+        <v>0.000563582195698578</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.0001854842375260116</v>
+        <v>0.0007213093493986245</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0001506800631396709</v>
+        <v>0.0005793549110685827</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0.0003646784048892946</v>
+        <v>0.0002700138780246768</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0001720798973146333</v>
+        <v>0.0005484208077641921</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>6.392197160117544e-05</v>
+        <v>0.0005057122465941025</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0001612641047432875</v>
+        <v>0.0005441499516471831</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>8.92462492968687e-05</v>
+        <v>0.0007860210257828102</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0001540623191986456</v>
+        <v>0.0005683370590607458</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>0.0001283056461090763</v>
+        <v>0.002023336091041215</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001514866518896887</v>
+        <v>0.0007138369622587929</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>0.0001289254118072909</v>
+        <v>0.001924364174408838</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001492305278814489</v>
+        <v>0.0008348896834737974</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>0.000285659737759948</v>
+        <v>0.0009905952450106263</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0001628734488692988</v>
+        <v>0.0008504602396274804</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.0003365821772610038</v>
+        <v>0.001232153285456882</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0001802443217084693</v>
+        <v>0.0008886295442104206</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>6.365958289399133e-05</v>
+        <v>0.001234609390133446</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0001685858478270215</v>
+        <v>0.0009232275288027232</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0.0002319817644785927</v>
+        <v>0.001717505354816117</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0001749254394921786</v>
+        <v>0.001002655311404063</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0.0002319817644785927</v>
+        <v>0.001717505354816117</v>
       </c>
       <c r="R33" t="n">
-        <v>0.00018063107199082</v>
+        <v>0.001074140315745268</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>9.750714380692526e-05</v>
+        <v>0.001441963876833363</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0001723186791724306</v>
+        <v>0.001110922671854078</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>0.0003655387789710372</v>
+        <v>0.0009606207138741922</v>
       </c>
       <c r="R35" t="n">
-        <v>0.0001916406891522912</v>
+        <v>0.001095892476056089</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>0.0004115168418799755</v>
+        <v>0.0008051738661154079</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0002136283044250597</v>
+        <v>0.001066820615062021</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>7.417263198115e-05</v>
+        <v>0.001120686031981444</v>
       </c>
       <c r="R37" t="n">
-        <v>0.0001996827371806687</v>
+        <v>0.001072207156753963</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>7.099530840637243e-05</v>
+        <v>0.001168119498347868</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0001868139943032391</v>
+        <v>0.001081798390913354</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>7.099545148029275e-05</v>
+        <v>0.001168119498347868</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0001752321400209444</v>
+        <v>0.001090430501656805</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>0.0001217214063314227</v>
+        <v>0.001775113807815057</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0001698810666519923</v>
+        <v>0.00115889883227263</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.0001346967203373943</v>
+        <v>0.002371693029030078</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0001663626320205325</v>
+        <v>0.001280178251948375</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>0.0002698314201447169</v>
+        <v>0.0003843719146575033</v>
       </c>
       <c r="R42" t="n">
-        <v>0.0001767095108329509</v>
+        <v>0.001190597618219288</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>7.691958680419134e-05</v>
+        <v>0.001091959901807887</v>
       </c>
       <c r="R43" t="n">
-        <v>0.0001667305184300749</v>
+        <v>0.001180733846578148</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>7.691958680419134e-05</v>
+        <v>0.001091959901807887</v>
       </c>
       <c r="R44" t="n">
-        <v>0.0001577494252674866</v>
+        <v>0.001171856452101122</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>9.614476033949656e-05</v>
+        <v>0.001546175528463384</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0001515889587746875</v>
+        <v>0.001209288359737348</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>0.0001471284848072574</v>
+        <v>0.001769694862410764</v>
       </c>
       <c r="R46" t="n">
-        <v>0.0001511429113779445</v>
+        <v>0.00126532901000469</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>0.0001277191342165318</v>
+        <v>0.001880994435402247</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0001488005336618033</v>
+        <v>0.001326895552544445</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>0.0001277191342165318</v>
+        <v>0.001880994435402247</v>
       </c>
       <c r="R48" t="n">
-        <v>0.0001466923937172761</v>
+        <v>0.001382305440830226</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>7.079627701943221e-05</v>
+        <v>0.0002818121096940968</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0001391027820474917</v>
+        <v>0.001272256107716613</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>6.645442898675989e-05</v>
+        <v>0.0004512544649184228</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0001318379467414185</v>
+        <v>0.001190155943436794</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>6.645442898675989e-05</v>
+        <v>0.0004512544649184228</v>
       </c>
       <c r="R51" t="n">
-        <v>0.0001252995949659526</v>
+        <v>0.001116265795584956</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>0.0001152318994222677</v>
+        <v>0.0008746691566892709</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0001242928254115841</v>
+        <v>0.001092106131695388</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>8.012226529876004e-05</v>
+        <v>0.0001958894093731341</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0001198757694003017</v>
+        <v>0.001002484459463162</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>0.0001437841263804884</v>
+        <v>0.0003264129237459881</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0001222666050983204</v>
+        <v>0.0009348773058914447</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>0.000635350118873387</v>
+        <v>0.001270689679478804</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0001735749564758271</v>
+        <v>0.0009684585432501806</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>6.237310191672058e-05</v>
+        <v>0.0008284923711789731</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0001624547710199165</v>
+        <v>0.0009544619260430598</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>5.718949501952701e-05</v>
+        <v>0.0007769697882999897</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0001519282434198775</v>
+        <v>0.0009367127122687528</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>0.0002429230898564454</v>
+        <v>0.0006750865313225328</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0001610277280635343</v>
+        <v>0.0009105500941741308</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>0.0001500031618278265</v>
+        <v>0.0005523975897543714</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0001599252714399635</v>
+        <v>0.0008747348437321548</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>0.0001500031618278265</v>
+        <v>0.0005523975897543714</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0001589330604787498</v>
+        <v>0.0008425011183343764</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>9.812585051230131e-05</v>
+        <v>0.0003342608164045369</v>
       </c>
       <c r="R61" t="n">
-        <v>0.000152852339482105</v>
+        <v>0.0007916770881413924</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>8.435544080199481e-05</v>
+        <v>0.0003854595409256427</v>
       </c>
       <c r="R62" t="n">
-        <v>0.000146002649614094</v>
+        <v>0.0007510553334198174</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>0.0001854504642448556</v>
+        <v>0.000797822140961553</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0001499474310771701</v>
+        <v>0.0007557320141739909</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>0.0004299813060805826</v>
+        <v>0.001066911280553395</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0001779508185775114</v>
+        <v>0.0007868499408119315</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0.0004280184865218721</v>
+        <v>0.001105333954665674</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0002029575853719475</v>
+        <v>0.0008186983421973058</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>7.573710271383467e-05</v>
+        <v>0.0005097493848677383</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0001902355371061362</v>
+        <v>0.000787803446464349</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>5.662618156497616e-05</v>
+        <v>0.0005492008456501208</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0001768746015520202</v>
+        <v>0.0007639431863829261</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>8.105943979487757e-05</v>
+        <v>0.001214831804730784</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0001672930853763059</v>
+        <v>0.0008090320482177121</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>0.0001915864574615847</v>
+        <v>0.0007876390235034764</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0001697224225848338</v>
+        <v>0.0008068927457462884</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>0.0001089540219103006</v>
+        <v>0.001150186553643956</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0001636455825173804</v>
+        <v>0.0008412221265360552</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>0.0001089543834745585</v>
+        <v>0.001150185807600094</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0001581764626130983</v>
+        <v>0.0008721184946424591</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>0.0001157249857922499</v>
+        <v>0.0007387431366074503</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0001539313149310134</v>
+        <v>0.0008587809588389583</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>0.0002942598381559892</v>
+        <v>0.0004867394045138917</v>
       </c>
       <c r="R73" t="n">
-        <v>0.000167964167253511</v>
+        <v>0.0008215768034064516</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>5.759542810526667e-05</v>
+        <v>0.0007689828842217708</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0001569272933386865</v>
+        <v>0.0008163174114879834</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>0.0002050910882329916</v>
+        <v>0.001149549546458737</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0001617436728281171</v>
+        <v>0.0008496406249850587</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0.007269544867775586</v>
+        <v>0.009016419557435715</v>
       </c>
       <c r="R76" t="n">
-        <v>0.0008725237923228643</v>
+        <v>0.001666318518230125</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>0.0001328469995788315</v>
+        <v>0.0002983728406543452</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0007985561130484611</v>
+        <v>0.001529523950472547</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>0.0001188886764478866</v>
+        <v>0.0009388266888933074</v>
       </c>
       <c r="R78" t="n">
-        <v>0.0007305893693884036</v>
+        <v>0.001470454224314623</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>8.018314440726468e-05</v>
+        <v>0.0008089953900943916</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0006655487468902896</v>
+        <v>0.0014043083408926</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>9.409692716484257e-05</v>
+        <v>0.0008077577328504996</v>
       </c>
       <c r="R80" t="n">
-        <v>0.0006084035649177448</v>
+        <v>0.00134465328008839</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0.0001356100786165906</v>
+        <v>0.001136649761978557</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0005611242162876294</v>
+        <v>0.001323852928277406</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>0.0001486888054341783</v>
+        <v>0.0006951240365835089</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0005198806752022843</v>
+        <v>0.001260980039108017</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>9.09355028951548e-05</v>
+        <v>0.0004766626827567583</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0004769861579715713</v>
+        <v>0.001182548303472891</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>8.706131293414756e-05</v>
+        <v>0.0008913322400503194</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0004379936734678289</v>
+        <v>0.001153426697130634</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>5.387333846687518e-05</v>
+        <v>0.0006103257592959345</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0003995816399677336</v>
+        <v>0.001099116603347164</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>5.387333846687518e-05</v>
+        <v>0.0006103257592959345</v>
       </c>
       <c r="R86" t="n">
-        <v>0.0003650108098176478</v>
+        <v>0.001050237518942041</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>0.0001314463279944189</v>
+        <v>0.0007752517390678999</v>
       </c>
       <c r="R87" t="n">
-        <v>0.0003416543616353249</v>
+        <v>0.001022738940954627</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0.0004741483636642853</v>
+        <v>0.001258134656628041</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0003549037618382209</v>
+        <v>0.001046278512521969</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0.0002079527706126707</v>
+        <v>0.0003455661438331832</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0003402086627156659</v>
+        <v>0.0009762072756530901</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>0.0001591316930133103</v>
+        <v>0.001307915862942988</v>
       </c>
       <c r="R90" t="n">
-        <v>0.0003221009657454304</v>
+        <v>0.00100937813438208</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>0.0001319175609583479</v>
+        <v>0.001352995632486187</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0003030826252667221</v>
+        <v>0.00104373988419249</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>8.199426135056734e-05</v>
+        <v>0.0004383041630190713</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0002809737888751066</v>
+        <v>0.0009831963120751485</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>8.516245822981874e-05</v>
+        <v>0.0006838582720409365</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0002613926558105779</v>
+        <v>0.0009532625080717275</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>0.0002322332582001577</v>
+        <v>0.001090490739844765</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0002584767160495359</v>
+        <v>0.0009669853312490312</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>0.0002511926306290661</v>
+        <v>0.0009799288045591352</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0002577483075074889</v>
+        <v>0.0009682796785800416</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>0.0001847377475349465</v>
+        <v>0.0006610411884751963</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0002504472515102347</v>
+        <v>0.0009375558295695571</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>0.0001471955245706403</v>
+        <v>0.0007309213090037867</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0002401220788162752</v>
+        <v>0.0009168923775129801</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0.0001471955245706403</v>
+        <v>0.0007309213090037867</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0002308294233917118</v>
+        <v>0.0008982952706620608</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>0.0001118295838109373</v>
+        <v>0.001190488624297932</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0002189294394336343</v>
+        <v>0.0009275146060256478</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>0.0002470339288273224</v>
+        <v>0.001199279069823254</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0002217398883730031</v>
+        <v>0.0009546910524054085</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>0.0002165386109544213</v>
+        <v>0.001234286805349758</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0002212197606311449</v>
+        <v>0.0009826506276998436</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>0.0001094230861384301</v>
+        <v>0.001101454534771614</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0002100400931818734</v>
+        <v>0.0009945310184070206</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>5.273265826027584e-05</v>
+        <v>0.0009478295994711964</v>
       </c>
       <c r="R103" t="n">
-        <v>0.0001943093496897137</v>
+        <v>0.0009898608765134382</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>9.578089715314738e-05</v>
+        <v>0.0007613754925065282</v>
       </c>
       <c r="R104" t="n">
-        <v>0.000184456504436057</v>
+        <v>0.0009670123381127473</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>0.0002717481187163978</v>
+        <v>0.001444305003444268</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0001931856658640911</v>
+        <v>0.001014741604645899</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>0.0004859360452890677</v>
+        <v>0.001198923451064758</v>
       </c>
       <c r="R106" t="n">
-        <v>0.0002224607038065888</v>
+        <v>0.001033159789287785</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>0.0004174930282047293</v>
+        <v>0.0009270427870584819</v>
       </c>
       <c r="R107" t="n">
-        <v>0.0002419639362464028</v>
+        <v>0.001022548089064855</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0.0001892295670458022</v>
+        <v>0.0009126379705923662</v>
       </c>
       <c r="R108" t="n">
-        <v>0.0002366904993263428</v>
+        <v>0.001011557077217606</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>5.750906059365663e-05</v>
+        <v>0.000655115418076132</v>
       </c>
       <c r="R109" t="n">
-        <v>0.0002187723554530741</v>
+        <v>0.0009759129113034585</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>7.416834310106267e-05</v>
+        <v>0.0009730301627765279</v>
       </c>
       <c r="R110" t="n">
-        <v>0.000204311954217873</v>
+        <v>0.0009756246364507655</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>0.0001820694547767257</v>
+        <v>0.001328635868321481</v>
       </c>
       <c r="R111" t="n">
-        <v>0.0002020877042737583</v>
+        <v>0.001010925759637837</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>0.0003476134610722821</v>
+        <v>0.0008222949862105982</v>
       </c>
       <c r="R112" t="n">
-        <v>0.0002166402799536107</v>
+        <v>0.0009920626822951134</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>0.0003476134610722821</v>
+        <v>0.0008222949862105982</v>
       </c>
       <c r="R113" t="n">
-        <v>0.0002297375980654778</v>
+        <v>0.0009750859126866618</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>0.0001284430220806979</v>
+        <v>0.0009058470839186382</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0002196081404669998</v>
+        <v>0.0009681620298098595</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -7700,10 +7700,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>8.718272317661945e-05</v>
+        <v>0.0007542138506284372</v>
       </c>
       <c r="R115" t="n">
-        <v>0.0002063655987379618</v>
+        <v>0.0009467672118917172</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>8.406828747295005e-05</v>
+        <v>0.001402200364688047</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0001941358676114606</v>
+        <v>0.0009923105271713501</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>0.000232533010458334</v>
+        <v>0.001361797513350657</v>
       </c>
       <c r="R117" t="n">
-        <v>0.000197975581896148</v>
+        <v>0.001029259225789281</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>0.0001424699251151544</v>
+        <v>0.0007848070224360699</v>
       </c>
       <c r="R118" t="n">
-        <v>0.0001924250162180486</v>
+        <v>0.00100481400545396</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0.0002115386180112833</v>
+        <v>0.0006099797299008855</v>
       </c>
       <c r="R119" t="n">
-        <v>0.0001943363763973721</v>
+        <v>0.0009653305778986524</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0.005132901724632266</v>
+        <v>0.00779438140214964</v>
       </c>
       <c r="R120" t="n">
-        <v>0.0006881929112208618</v>
+        <v>0.001648235660323751</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>6.813316879579351e-05</v>
+        <v>0.0006539048558127304</v>
       </c>
       <c r="R121" t="n">
-        <v>0.000626186936978355</v>
+        <v>0.001548802579872649</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>6.813316879579351e-05</v>
+        <v>0.0006539048558127304</v>
       </c>
       <c r="R122" t="n">
-        <v>0.0005703815601600989</v>
+        <v>0.001459312807466657</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>0.0002226005016517782</v>
+        <v>0.001256181067450175</v>
       </c>
       <c r="R123" t="n">
-        <v>0.0005356034543092667</v>
+        <v>0.001438999633465009</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>0.0001436832793814934</v>
+        <v>0.0009311971601996845</v>
       </c>
       <c r="R124" t="n">
-        <v>0.0004964114368164893</v>
+        <v>0.001388219386138477</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0.000176489455473097</v>
+        <v>0.0006388704862292006</v>
       </c>
       <c r="R125" t="n">
-        <v>0.0004644192386821501</v>
+        <v>0.001313284496147549</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -8393,10 +8393,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>0.002846125095665578</v>
+        <v>0.004515263610568284</v>
       </c>
       <c r="R126" t="n">
-        <v>0.000702589824380493</v>
+        <v>0.001633482407589623</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>0.0001145274481807576</v>
+        <v>0.001251929397521548</v>
       </c>
       <c r="R127" t="n">
-        <v>0.0006437835867605195</v>
+        <v>0.001595327106582815</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>0.0001771905471882368</v>
+        <v>0.001007474638855447</v>
       </c>
       <c r="R128" t="n">
-        <v>0.0005971242828032912</v>
+        <v>0.001536541859810078</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>0.0002506819896443313</v>
+        <v>0.0005722073330416356</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0005624800534873951</v>
+        <v>0.001440108407133234</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>0.0001466720942918548</v>
+        <v>0.0005940835181174347</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0005208992575678411</v>
+        <v>0.001355505918231654</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>9.067359358894454e-05</v>
+        <v>0.0004737885038853951</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0004778766911699515</v>
+        <v>0.001267334176797028</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>5.147185729694666e-05</v>
+        <v>0.0004671384455279942</v>
       </c>
       <c r="R132" t="n">
-        <v>0.000435236207782651</v>
+        <v>0.001187314603670125</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>0.0001617936409158581</v>
+        <v>0.001557037811918716</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0004078919510959717</v>
+        <v>0.001224286924494984</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>0.0008695811129075063</v>
+        <v>0.002220391776226944</v>
       </c>
       <c r="R134" t="n">
-        <v>0.0004540608672771252</v>
+        <v>0.00132389740966818</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>0.001134677790610711</v>
+        <v>0.001934221211809118</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0005221225596104838</v>
+        <v>0.001384929789882273</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>0.0001018986368191818</v>
+        <v>0.0007544843555504912</v>
       </c>
       <c r="R136" t="n">
-        <v>0.0004801001673313536</v>
+        <v>0.001321885246449095</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>0.0001018980138105053</v>
+        <v>0.0007544853642183875</v>
       </c>
       <c r="R137" t="n">
-        <v>0.0004422799519792688</v>
+        <v>0.001265145258226024</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0.000459766604165052</v>
+        <v>0.001032746315054868</v>
       </c>
       <c r="R138" t="n">
-        <v>0.000444028617197847</v>
+        <v>0.001241905363908909</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>0.0001562287198734598</v>
+        <v>0.001073098309606926</v>
       </c>
       <c r="R139" t="n">
-        <v>0.0004152486274654083</v>
+        <v>0.001225024658478711</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -9275,10 +9275,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>0.001042127966237216</v>
+        <v>0.001979760165425434</v>
       </c>
       <c r="R140" t="n">
-        <v>0.000477936561342589</v>
+        <v>0.001300498209173383</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>0.001158196533405547</v>
+        <v>0.001997785380982562</v>
       </c>
       <c r="R141" t="n">
-        <v>0.0005459625585488849</v>
+        <v>0.001370226926354301</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>0.0001175875947136832</v>
+        <v>0.001196479023012001</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0005031250621653648</v>
+        <v>0.001352852136020071</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>8.232273087531093e-05</v>
+        <v>0.001425976114613065</v>
       </c>
       <c r="R143" t="n">
-        <v>0.0004610448290363594</v>
+        <v>0.00136016453387937</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>8.400273851875601e-05</v>
+        <v>0.001355966694015377</v>
       </c>
       <c r="R144" t="n">
-        <v>0.0004233406199845991</v>
+        <v>0.001359744749892971</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -9590,10 +9590,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>0.000103481225987954</v>
+        <v>0.001663207972457002</v>
       </c>
       <c r="R145" t="n">
-        <v>0.0003913546805849346</v>
+        <v>0.001390091072149374</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>0.000294228360556053</v>
+        <v>0.0009794025354989302</v>
       </c>
       <c r="R146" t="n">
-        <v>0.0003816420485820464</v>
+        <v>0.001349022218484329</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>0.001057368802446616</v>
+        <v>0.001512418916647053</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0004492147239685035</v>
+        <v>0.001365361888300602</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -9779,14 +9779,14 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>0.02390034877555321</v>
+        <v>0.02411072595895537</v>
       </c>
       <c r="R148" t="n">
-        <v>0.002794328129126975</v>
+        <v>0.00363989829536608</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -9842,14 +9842,14 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>7.258390638679684e-05</v>
+        <v>0.001589068864227317</v>
       </c>
       <c r="R149" t="n">
-        <v>0.002522153706852957</v>
+        <v>0.003434815352252203</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -9905,14 +9905,14 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>6.422503545473708e-05</v>
+        <v>0.00151684915672648</v>
       </c>
       <c r="R150" t="n">
-        <v>0.002276360839713135</v>
+        <v>0.003243018732699631</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -9968,14 +9968,14 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>0.0001404904879995817</v>
+        <v>0.002403459045842727</v>
       </c>
       <c r="R151" t="n">
-        <v>0.00206277380454178</v>
+        <v>0.00315906276401394</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10031,14 +10031,14 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>0.0006015047752234489</v>
+        <v>0.002598718844905326</v>
       </c>
       <c r="R152" t="n">
-        <v>0.001916646901609947</v>
+        <v>0.003103028372103079</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10094,14 +10094,14 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>0.0006015047752234489</v>
+        <v>0.002598718844905326</v>
       </c>
       <c r="R153" t="n">
-        <v>0.001785132688971297</v>
+        <v>0.003052597419383303</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10157,14 +10157,14 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>0.0001699404367670024</v>
+        <v>0.0008197224602284519</v>
       </c>
       <c r="R154" t="n">
-        <v>0.001623613463750867</v>
+        <v>0.002829309923467818</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10220,14 +10220,14 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>7.625950669089347e-05</v>
+        <v>0.001229148558497335</v>
       </c>
       <c r="R155" t="n">
-        <v>0.00146887806804487</v>
+        <v>0.002669293786970769</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10283,14 +10283,14 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>7.625950669089347e-05</v>
+        <v>0.001229148558497335</v>
       </c>
       <c r="R156" t="n">
-        <v>0.001329616211909472</v>
+        <v>0.002525279264123426</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Warning (Yellow) - Operational Drift</t>
+          <t>Normal (Green)</t>
         </is>
       </c>
     </row>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>0.0001676000095279414</v>
+        <v>0.001559694393889174</v>
       </c>
       <c r="R157" t="n">
-        <v>0.001213414591671319</v>
+        <v>0.002428720777100001</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>0.0006925751079731393</v>
+        <v>0.003805527076391317</v>
       </c>
       <c r="R158" t="n">
-        <v>0.001161330643301501</v>
+        <v>0.002566401407029132</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>0.00162329045878073</v>
+        <v>0.002719594598286013</v>
       </c>
       <c r="R159" t="n">
-        <v>0.001207526624849424</v>
+        <v>0.00258172072615482</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>0.0001537842742130978</v>
+        <v>0.0011211531247161</v>
       </c>
       <c r="R160" t="n">
-        <v>0.001102152389785791</v>
+        <v>0.002435663966010948</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>0.0002429525805789278</v>
+        <v>0.001211766204379419</v>
       </c>
       <c r="R161" t="n">
-        <v>0.001016232408865105</v>
+        <v>0.002313274189847795</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -10661,10 +10661,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>0.0001396065425054558</v>
+        <v>0.001348085998934748</v>
       </c>
       <c r="R162" t="n">
-        <v>0.0009285698222291397</v>
+        <v>0.002216755370756491</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>9.212184503542538e-05</v>
+        <v>0.001765692593266545</v>
       </c>
       <c r="R163" t="n">
-        <v>0.0008449250245097683</v>
+        <v>0.002171649093007496</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>0.001738095800234838</v>
+        <v>0.002793596377840594</v>
       </c>
       <c r="R164" t="n">
-        <v>0.0009342421020822753</v>
+        <v>0.002233843821490806</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -10850,10 +10850,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>0.001729180405436575</v>
+        <v>0.002854452296021406</v>
       </c>
       <c r="R165" t="n">
-        <v>0.001013735932417705</v>
+        <v>0.002295904668943866</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>8.54478317284936e-05</v>
+        <v>0.001762601792550337</v>
       </c>
       <c r="R166" t="n">
-        <v>0.0009209071223487842</v>
+        <v>0.002242574381304513</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>0.0001519210811031591</v>
+        <v>0.001282742677135419</v>
       </c>
       <c r="R167" t="n">
-        <v>0.0008440085182242215</v>
+        <v>0.002146591210887604</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>9.486375677139662e-05</v>
+        <v>0.001324972802587146</v>
       </c>
       <c r="R168" t="n">
-        <v>0.0007690940420789391</v>
+        <v>0.002064429370057558</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>0.0001005350464242359</v>
+        <v>0.001492606150572098</v>
       </c>
       <c r="R169" t="n">
-        <v>0.0007022381425134687</v>
+        <v>0.002007247048109012</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -11165,10 +11165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>0.0007978926240630293</v>
+        <v>0.002129256239014409</v>
       </c>
       <c r="R170" t="n">
-        <v>0.0007118035906684247</v>
+        <v>0.002019447967199551</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -11228,10 +11228,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>0.0004561785329474761</v>
+        <v>0.00305081426003749</v>
       </c>
       <c r="R171" t="n">
-        <v>0.0006862410848963297</v>
+        <v>0.002122584596483345</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -11291,10 +11291,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>7.408038891277045e-05</v>
+        <v>0.001066983289209595</v>
       </c>
       <c r="R172" t="n">
-        <v>0.0006250250152979738</v>
+        <v>0.00201702446575597</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>8.334862849310554e-05</v>
+        <v>0.001163408289890277</v>
       </c>
       <c r="R173" t="n">
-        <v>0.0005708573766174869</v>
+        <v>0.001931662848169401</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>8.266568561971643e-05</v>
+        <v>0.001557147432199718</v>
       </c>
       <c r="R174" t="n">
-        <v>0.0005220382075177098</v>
+        <v>0.001894211306572433</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>0.00015869491466317</v>
+        <v>0.001483949634025213</v>
       </c>
       <c r="R175" t="n">
-        <v>0.0004857038782322558</v>
+        <v>0.001853185139317711</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>0.0007284400303122065</v>
+        <v>0.001714295974718121</v>
       </c>
       <c r="R176" t="n">
-        <v>0.0005099774934402508</v>
+        <v>0.001839296222857752</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -11606,10 +11606,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>0.0007284400303122065</v>
+        <v>0.001714295974718121</v>
       </c>
       <c r="R177" t="n">
-        <v>0.0005318237471274463</v>
+        <v>0.001826796198043789</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>8.619023433081867e-05</v>
+        <v>0.001313268875201991</v>
       </c>
       <c r="R178" t="n">
-        <v>0.0004872603958477835</v>
+        <v>0.001775443465759609</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -11732,10 +11732,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>7.408965432623759e-05</v>
+        <v>0.002158369362906028</v>
       </c>
       <c r="R179" t="n">
-        <v>0.0004459433216956288</v>
+        <v>0.001813736055474251</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>

--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output5.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_generator_bearings_deviation_monitoring/deviation_monitoring/dsas_g11_generator_bearings_deviation_monitoring_output5.xlsx
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005599550529367897</v>
+        <v>0.0002300194885403827</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0008870771030177027</v>
+        <v>0.0004168117848368027</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005599550529367897</v>
+        <v>0.0002300194885403827</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008543648980096114</v>
+        <v>0.0003981325552071607</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007505040559887258</v>
+        <v>0.0002718768284922588</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0008439788138075228</v>
+        <v>0.0003855069825356705</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.000378216583513647</v>
+        <v>0.0009356417766905769</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0007974025907781352</v>
+        <v>0.0004405204619511612</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001648098577340351</v>
+        <v>0.0003480134438071795</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007341433174737252</v>
+        <v>0.0004312697601367631</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.000402408521969925</v>
+        <v>0.0002663983454869046</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0007009698379233451</v>
+        <v>0.0004147826186717772</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.0004905272867109583</v>
+        <v>0.0002071915618417961</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0006799255828021064</v>
+        <v>0.0003940235129887791</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0.0004919456689275297</v>
+        <v>0.0002104006285672204</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006611275914146488</v>
+        <v>0.0003756612245466233</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0.000626816282822863</v>
+        <v>0.0005060411339270107</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0006576964605554702</v>
+        <v>0.000388699215484662</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.0005700366779007263</v>
+        <v>0.000854025937961941</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0006489304822899957</v>
+        <v>0.0004352318877323899</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.0003623421596286699</v>
+        <v>0.0002943065138308743</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0006202716500238631</v>
+        <v>0.0004211393503422383</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0.0002882772303515796</v>
+        <v>0.0002321836295851609</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0005870722080566348</v>
+        <v>0.0004022437782665306</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.000453850707320261</v>
+        <v>0.0001153635243887679</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005737500579829974</v>
+        <v>0.0003735557528787543</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.000453850707320261</v>
+        <v>0.0001153635243887679</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0005617601229167237</v>
+        <v>0.0003477365300297557</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>0.0007274783851394875</v>
+        <v>0.001140852770418258</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0005783319491390001</v>
+        <v>0.0004270481540686059</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0.0006699809713196849</v>
+        <v>0.0009815721901305346</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0005874968513570686</v>
+        <v>0.0004825005576747988</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.0003700899334545618</v>
+        <v>0.0002010678978474873</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0005657561595668178</v>
+        <v>0.0004543572916920676</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>0.0004658941322448205</v>
+        <v>0.0003173396455876793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0005557699568346182</v>
+        <v>0.0004406555270816288</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>0.0004658941322448205</v>
+        <v>0.0003173396455876793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0005467823743756385</v>
+        <v>0.0004283239389322338</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>0.0005395281946049808</v>
+        <v>0.0001163223357662818</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0005460569563985727</v>
+        <v>0.0003971237786156386</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>0.0007213093493986245</v>
+        <v>0.0009304213909326893</v>
       </c>
       <c r="R22" t="n">
-        <v>0.000563582195698578</v>
+        <v>0.0004504535398473437</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.0007213093493986245</v>
+        <v>0.0009304213909326893</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0005793549110685827</v>
+        <v>0.0004984503249558782</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0.0002700138780246768</v>
+        <v>0.0003890277991941806</v>
       </c>
       <c r="R24" t="n">
-        <v>0.0005484208077641921</v>
+        <v>0.0004875080723797085</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>0.0005057122465941025</v>
+        <v>0.000100450458448764</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0005441499516471831</v>
+        <v>0.000448802310986614</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>0.0007860210257828102</v>
+        <v>9.807023285302588e-05</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0005683370590607458</v>
+        <v>0.0004137291031732551</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>0.002023336091041215</v>
+        <v>0.0002645276812111156</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0007138369622587929</v>
+        <v>0.0003988089609770412</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>0.001924364174408838</v>
+        <v>0.000963441136453007</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0008348896834737974</v>
+        <v>0.0004552721785246377</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>0.0009905952450106263</v>
+        <v>0.0009760813609688489</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0008504602396274804</v>
+        <v>0.0005073530967690589</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.001232153285456882</v>
+        <v>0.001466603748926674</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0008886295442104206</v>
+        <v>0.0006032781619848206</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>0.001234609390133446</v>
+        <v>0.000227020959560153</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0009232275288027232</v>
+        <v>0.0005656524417423539</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0.001717505354816117</v>
+        <v>0.0003211682181584695</v>
       </c>
       <c r="R32" t="n">
-        <v>0.001002655311404063</v>
+        <v>0.0005412040193839655</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0.001717505354816117</v>
+        <v>0.0003211682181584695</v>
       </c>
       <c r="R33" t="n">
-        <v>0.001074140315745268</v>
+        <v>0.0005192004392614158</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>0.001441963876833363</v>
+        <v>0.0004232171613342594</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001110922671854078</v>
+        <v>0.0005096021114687001</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>0.0009606207138741922</v>
+        <v>0.0008656101709176097</v>
       </c>
       <c r="R35" t="n">
-        <v>0.001095892476056089</v>
+        <v>0.000545202917413591</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>0.0008051738661154079</v>
+        <v>0.0003098937279848153</v>
       </c>
       <c r="R36" t="n">
-        <v>0.001066820615062021</v>
+        <v>0.0005216719984707135</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>0.001120686031981444</v>
+        <v>0.000132485145938745</v>
       </c>
       <c r="R37" t="n">
-        <v>0.001072207156753963</v>
+        <v>0.0004827533132175167</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>0.001168119498347868</v>
+        <v>0.0001750240761943546</v>
       </c>
       <c r="R38" t="n">
-        <v>0.001081798390913354</v>
+        <v>0.0004519803895152005</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>0.001168119498347868</v>
+        <v>0.0001750238697335522</v>
       </c>
       <c r="R39" t="n">
-        <v>0.001090430501656805</v>
+        <v>0.0004242847375370356</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>0.001775113807815057</v>
+        <v>0.0007154374367735005</v>
       </c>
       <c r="R40" t="n">
-        <v>0.00115889883227263</v>
+        <v>0.0004534000074606821</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.002371693029030078</v>
+        <v>0.002595555129042097</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001280178251948375</v>
+        <v>0.0006676155196188238</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>0.0003843719146575033</v>
+        <v>0.0001581196194669688</v>
       </c>
       <c r="R42" t="n">
-        <v>0.001190597618219288</v>
+        <v>0.0006166659296036383</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>0.001091959901807887</v>
+        <v>0.0001155591442808029</v>
       </c>
       <c r="R43" t="n">
-        <v>0.001180733846578148</v>
+        <v>0.0005665552510713547</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>0.001091959901807887</v>
+        <v>0.0001155591442808029</v>
       </c>
       <c r="R44" t="n">
-        <v>0.001171856452101122</v>
+        <v>0.0005214556403922995</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>0.001546175528463384</v>
+        <v>0.0001033154859104757</v>
       </c>
       <c r="R45" t="n">
-        <v>0.001209288359737348</v>
+        <v>0.0004796416249441171</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>0.001769694862410764</v>
+        <v>0.0007460896294673573</v>
       </c>
       <c r="R46" t="n">
-        <v>0.00126532901000469</v>
+        <v>0.0005062864253964412</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>0.001880994435402247</v>
+        <v>0.0006946482423823898</v>
       </c>
       <c r="R47" t="n">
-        <v>0.001326895552544445</v>
+        <v>0.0005251226070950361</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>0.001880994435402247</v>
+        <v>0.0006946482423823898</v>
       </c>
       <c r="R48" t="n">
-        <v>0.001382305440830226</v>
+        <v>0.0005420751706237714</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>0.0002818121096940968</v>
+        <v>0.0001283235727123736</v>
       </c>
       <c r="R49" t="n">
-        <v>0.001272256107716613</v>
+        <v>0.0005007000108326316</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>0.0004512544649184228</v>
+        <v>0.0001765403156043287</v>
       </c>
       <c r="R50" t="n">
-        <v>0.001190155943436794</v>
+        <v>0.0004682840413098013</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>0.0004512544649184228</v>
+        <v>0.0001765403156043287</v>
       </c>
       <c r="R51" t="n">
-        <v>0.001116265795584956</v>
+        <v>0.000439109668739254</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>0.0008746691566892709</v>
+        <v>0.0004987461867889948</v>
       </c>
       <c r="R52" t="n">
-        <v>0.001092106131695388</v>
+        <v>0.000445073320544228</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>0.0001958894093731341</v>
+        <v>0.0003509306493944622</v>
       </c>
       <c r="R53" t="n">
-        <v>0.001002484459463162</v>
+        <v>0.0004356590534292514</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>0.0003264129237459881</v>
+        <v>0.0001459420119404708</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0009348773058914447</v>
+        <v>0.0004066873492803734</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>0.001270689679478804</v>
+        <v>0.0009990256480406632</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0009684585432501806</v>
+        <v>0.0004659211791564024</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>0.0008284923711789731</v>
+        <v>0.0001572752563568225</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0009544619260430598</v>
+        <v>0.0004350565868764444</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>0.0007769697882999897</v>
+        <v>0.0001499605404677294</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0009367127122687528</v>
+        <v>0.000406546982235573</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>0.0006750865313225328</v>
+        <v>0.0007416979266838098</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0009105500941741308</v>
+        <v>0.0004400620766803966</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>0.0005523975897543714</v>
+        <v>0.000555270789812557</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0008747348437321548</v>
+        <v>0.0004515829479936127</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -4235,10 +4235,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>0.0005523975897543714</v>
+        <v>0.000555270789812557</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0008425011183343764</v>
+        <v>0.0004619517321755071</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>0.0003342608164045369</v>
+        <v>0.0002542998090047745</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0007916770881413924</v>
+        <v>0.0004411865398584338</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>0.0003854595409256427</v>
+        <v>0.0002329280323293283</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0007510553334198174</v>
+        <v>0.0004203606891055232</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>0.000797822140961553</v>
+        <v>0.0007209031638961388</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0007557320141739909</v>
+        <v>0.0004504149365845848</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>0.001066911280553395</v>
+        <v>0.0008731856665717988</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0007868499408119315</v>
+        <v>0.0004926920095833062</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0.001105333954665674</v>
+        <v>0.0004063200993769881</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0008186983421973058</v>
+        <v>0.0004840548185626744</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>0.0005097493848677383</v>
+        <v>0.0002396218248003186</v>
       </c>
       <c r="R66" t="n">
-        <v>0.000787803446464349</v>
+        <v>0.0004596115191864389</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>0.0005492008456501208</v>
+        <v>0.0002187552115203589</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0007639431863829261</v>
+        <v>0.0004355258884198308</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>0.001214831804730784</v>
+        <v>0.0002477744947913057</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0008090320482177121</v>
+        <v>0.0004167507490569782</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>0.0007876390235034764</v>
+        <v>0.0007797057645328361</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0008068927457462884</v>
+        <v>0.0004530462506045641</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>0.001150186553643956</v>
+        <v>0.0006790584919580823</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0008412221265360552</v>
+        <v>0.0004756474747399159</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>0.001150185807600094</v>
+        <v>0.000679058273885557</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0008721184946424591</v>
+        <v>0.0004959885546544801</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>0.0007387431366074503</v>
+        <v>0.0004861220158456341</v>
       </c>
       <c r="R72" t="n">
-        <v>0.0008587809588389583</v>
+        <v>0.0004950019007735954</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>0.0004867394045138917</v>
+        <v>0.0006715075141189547</v>
       </c>
       <c r="R73" t="n">
-        <v>0.0008215768034064516</v>
+        <v>0.0005126524621081313</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>0.0007689828842217708</v>
+        <v>8.711390308607274e-05</v>
       </c>
       <c r="R74" t="n">
-        <v>0.0008163174114879834</v>
+        <v>0.0004700986062059254</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>0.001149549546458737</v>
+        <v>0.000908128579772576</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0008496406249850587</v>
+        <v>0.0005139016035625905</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>0.009016419557435715</v>
+        <v>0.00745052253532061</v>
       </c>
       <c r="R76" t="n">
-        <v>0.001666318518230125</v>
+        <v>0.001207563696738393</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -5306,10 +5306,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>0.0002983728406543452</v>
+        <v>0.0001857614403164593</v>
       </c>
       <c r="R77" t="n">
-        <v>0.001529523950472547</v>
+        <v>0.0011053834710962</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>0.0009388266888933074</v>
+        <v>0.0004993380602548741</v>
       </c>
       <c r="R78" t="n">
-        <v>0.001470454224314623</v>
+        <v>0.001044778930012067</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>0.0008089953900943916</v>
+        <v>0.0003076106463071528</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0014043083408926</v>
+        <v>0.0009710621016415755</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>0.0008077577328504996</v>
+        <v>0.0003447194635934107</v>
       </c>
       <c r="R80" t="n">
-        <v>0.00134465328008839</v>
+        <v>0.000908427837836759</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0.001136649761978557</v>
+        <v>0.0009129184825674241</v>
       </c>
       <c r="R81" t="n">
-        <v>0.001323852928277406</v>
+        <v>0.0009088769023098256</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>0.0006951240365835089</v>
+        <v>0.0007812159071699004</v>
       </c>
       <c r="R82" t="n">
-        <v>0.001260980039108017</v>
+        <v>0.000896110802795833</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>0.0004766626827567583</v>
+        <v>0.0003208993762826995</v>
       </c>
       <c r="R83" t="n">
-        <v>0.001182548303472891</v>
+        <v>0.0008385896601445195</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>0.0008913322400503194</v>
+        <v>0.0003776975317814748</v>
       </c>
       <c r="R84" t="n">
-        <v>0.001153426697130634</v>
+        <v>0.000792500447308215</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>0.0006103257592959345</v>
+        <v>0.0001665416524149469</v>
       </c>
       <c r="R85" t="n">
-        <v>0.001099116603347164</v>
+        <v>0.0007299045678188882</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>0.0006103257592959345</v>
+        <v>0.0001665416524149469</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001050237518942041</v>
+        <v>0.0006735682762784942</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>0.0007752517390678999</v>
+        <v>0.0004385621432251484</v>
       </c>
       <c r="R87" t="n">
-        <v>0.001022738940954627</v>
+        <v>0.0006500676629731596</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -5999,10 +5999,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>0.001258134656628041</v>
+        <v>0.001643451247869706</v>
       </c>
       <c r="R88" t="n">
-        <v>0.001046278512521969</v>
+        <v>0.0007494060214628144</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0.0003455661438331832</v>
+        <v>0.0001566860105195771</v>
       </c>
       <c r="R89" t="n">
-        <v>0.0009762072756530901</v>
+        <v>0.0006901340203684905</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>0.001307915862942988</v>
+        <v>0.0007527302234116158</v>
       </c>
       <c r="R90" t="n">
-        <v>0.00100937813438208</v>
+        <v>0.000696393640672803</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>0.001352995632486187</v>
+        <v>0.0006698331751566292</v>
       </c>
       <c r="R91" t="n">
-        <v>0.00104373988419249</v>
+        <v>0.0006937375941211857</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>0.0004383041630190713</v>
+        <v>0.0001951491769590421</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0009831963120751485</v>
+        <v>0.0006438787524049713</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>0.0006838582720409365</v>
+        <v>0.0003284045305384864</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0009532625080717275</v>
+        <v>0.0006123313302183228</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>0.001090490739844765</v>
+        <v>0.0008583380154037337</v>
       </c>
       <c r="R94" t="n">
-        <v>0.0009669853312490312</v>
+        <v>0.0006369319987368639</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>0.0009799288045591352</v>
+        <v>0.0008419905916644704</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0009682796785800416</v>
+        <v>0.0006574378580296245</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>0.0006610411884751963</v>
+        <v>0.0003532203473502187</v>
       </c>
       <c r="R96" t="n">
-        <v>0.0009375558295695571</v>
+        <v>0.0006270161069616839</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>0.0007309213090037867</v>
+        <v>0.000330393149775797</v>
       </c>
       <c r="R97" t="n">
-        <v>0.0009168923775129801</v>
+        <v>0.0005973538112430951</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>0.0007309213090037867</v>
+        <v>0.000330393149775797</v>
       </c>
       <c r="R98" t="n">
-        <v>0.0008982952706620608</v>
+        <v>0.0005706577450963653</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>0.001190488624297932</v>
+        <v>0.0003627531747076788</v>
       </c>
       <c r="R99" t="n">
-        <v>0.0009275146060256478</v>
+        <v>0.0005498672880574966</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>0.001199279069823254</v>
+        <v>0.0009910652509564268</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0009546910524054085</v>
+        <v>0.0005939870843473897</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>0.001234286805349758</v>
+        <v>0.0009398515259191422</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0009826506276998436</v>
+        <v>0.0006285735285045649</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>0.001101454534771614</v>
+        <v>0.0003499780371263852</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0009945310184070206</v>
+        <v>0.0006007139793667469</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>0.0009478295994711964</v>
+        <v>5.905372822350464e-05</v>
       </c>
       <c r="R103" t="n">
-        <v>0.0009898608765134382</v>
+        <v>0.0005465479542524227</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>0.0007613754925065282</v>
+        <v>0.0001229369936657893</v>
       </c>
       <c r="R104" t="n">
-        <v>0.0009670123381127473</v>
+        <v>0.0005041868581937593</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>0.001444305003444268</v>
+        <v>0.0009391024450371219</v>
       </c>
       <c r="R105" t="n">
-        <v>0.001014741604645899</v>
+        <v>0.0005476784168780955</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>0.001198923451064758</v>
+        <v>0.001009636954500306</v>
       </c>
       <c r="R106" t="n">
-        <v>0.001033159789287785</v>
+        <v>0.0005938742706403167</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -7196,10 +7196,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>0.0009270427870584819</v>
+        <v>0.001026864042765827</v>
       </c>
       <c r="R107" t="n">
-        <v>0.001022548089064855</v>
+        <v>0.0006371732478528678</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>0.0009126379705923662</v>
+        <v>0.0005387486166983976</v>
       </c>
       <c r="R108" t="n">
-        <v>0.001011557077217606</v>
+        <v>0.0006273307847374207</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>0.000655115418076132</v>
+        <v>0.0001328477865164929</v>
       </c>
       <c r="R109" t="n">
-        <v>0.0009759129113034585</v>
+        <v>0.0005778824849153279</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>0.0009730301627765279</v>
+        <v>8.064788988522181e-05</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0009756246364507655</v>
+        <v>0.0005281590254123173</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>0.001328635868321481</v>
+        <v>0.0006317203208706453</v>
       </c>
       <c r="R111" t="n">
-        <v>0.001010925759637837</v>
+        <v>0.0005385151549581501</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -7511,10 +7511,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>0.0008222949862105982</v>
+        <v>0.001153165442123603</v>
       </c>
       <c r="R112" t="n">
-        <v>0.0009920626822951134</v>
+        <v>0.0005999801836746953</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>0.0008222949862105982</v>
+        <v>0.001153165442123603</v>
       </c>
       <c r="R113" t="n">
-        <v>0.0009750859126866618</v>
+        <v>0.000655298709519586</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -7637,10 +7637,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>0.0009058470839186382</v>
+        <v>0.0005562214622677715</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0009681620298098595</v>
+        <v>0.0006453909847944046</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -7700,10 +7700,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>0.0007542138506284372</v>
+        <v>0.0003000018212763629</v>
       </c>
       <c r="R115" t="n">
-        <v>0.0009467672118917172</v>
+        <v>0.0006108520684426005</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>0.001402200364688047</v>
+        <v>0.0004106229469450838</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0009923105271713501</v>
+        <v>0.0005908291562928489</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>0.001361797513350657</v>
+        <v>0.0007086972401250347</v>
       </c>
       <c r="R117" t="n">
-        <v>0.001029259225789281</v>
+        <v>0.0006026159646760675</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>0.0007848070224360699</v>
+        <v>0.0004166337255503831</v>
       </c>
       <c r="R118" t="n">
-        <v>0.00100481400545396</v>
+        <v>0.0005840177407634991</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>0.0006099797299008855</v>
+        <v>0.0004667483494694145</v>
       </c>
       <c r="R119" t="n">
-        <v>0.0009653305778986524</v>
+        <v>0.0005722908016340906</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>0.00779438140214964</v>
+        <v>0.004379608979427324</v>
       </c>
       <c r="R120" t="n">
-        <v>0.001648235660323751</v>
+        <v>0.0009530226194134142</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>0.0006539048558127304</v>
+        <v>0.0001772507436460026</v>
       </c>
       <c r="R121" t="n">
-        <v>0.001548802579872649</v>
+        <v>0.0008754454318366731</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>0.0006539048558127304</v>
+        <v>0.0001772507436460026</v>
       </c>
       <c r="R122" t="n">
-        <v>0.001459312807466657</v>
+        <v>0.0008056259630176059</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>0.001256181067450175</v>
+        <v>0.000836360262016696</v>
       </c>
       <c r="R123" t="n">
-        <v>0.001438999633465009</v>
+        <v>0.0008086993929175148</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>0.0009311971601996845</v>
+        <v>0.0006175582550147406</v>
       </c>
       <c r="R124" t="n">
-        <v>0.001388219386138477</v>
+        <v>0.0007895852791272373</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0.0006388704862292006</v>
+        <v>0.0002619667316053672</v>
       </c>
       <c r="R125" t="n">
-        <v>0.001313284496147549</v>
+        <v>0.0007368234243750502</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -8393,10 +8393,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>0.004515263610568284</v>
+        <v>0.004681546002620554</v>
       </c>
       <c r="R126" t="n">
-        <v>0.001633482407589623</v>
+        <v>0.001131295682199601</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>0.001251929397521548</v>
+        <v>0.000497054369480572</v>
       </c>
       <c r="R127" t="n">
-        <v>0.001595327106582815</v>
+        <v>0.001067871550927698</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>0.001007474638855447</v>
+        <v>0.0006746093591166783</v>
       </c>
       <c r="R128" t="n">
-        <v>0.001536541859810078</v>
+        <v>0.001028545331746596</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>0.0005722073330416356</v>
+        <v>0.0008153175849388333</v>
       </c>
       <c r="R129" t="n">
-        <v>0.001440108407133234</v>
+        <v>0.00100722255706582</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>0.0005940835181174347</v>
+        <v>0.0006079260688763151</v>
       </c>
       <c r="R130" t="n">
-        <v>0.001355505918231654</v>
+        <v>0.000967292908246869</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>0.0004737885038853951</v>
+        <v>0.0002742898220197892</v>
       </c>
       <c r="R131" t="n">
-        <v>0.001267334176797028</v>
+        <v>0.0008979925996241611</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -8771,10 +8771,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>0.0004671384455279942</v>
+        <v>0.0001236666132853516</v>
       </c>
       <c r="R132" t="n">
-        <v>0.001187314603670125</v>
+        <v>0.00082056000099028</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>0.001557037811918716</v>
+        <v>0.0007621579388733474</v>
       </c>
       <c r="R133" t="n">
-        <v>0.001224286924494984</v>
+        <v>0.0008147197947785867</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>0.002220391776226944</v>
+        <v>0.0008251160303169912</v>
       </c>
       <c r="R134" t="n">
-        <v>0.00132389740966818</v>
+        <v>0.0008157594183324272</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>0.001934221211809118</v>
+        <v>0.0009760006614025715</v>
       </c>
       <c r="R135" t="n">
-        <v>0.001384929789882273</v>
+        <v>0.0008317835426394416</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>0.0007544843555504912</v>
+        <v>0.0005834469833911828</v>
       </c>
       <c r="R136" t="n">
-        <v>0.001321885246449095</v>
+        <v>0.0008069498867146157</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>0.0007544853642183875</v>
+        <v>0.0005834465864493224</v>
       </c>
       <c r="R137" t="n">
-        <v>0.001265145258226024</v>
+        <v>0.0007845995566880863</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>0.001032746315054868</v>
+        <v>0.0003684473216585724</v>
       </c>
       <c r="R138" t="n">
-        <v>0.001241905363908909</v>
+        <v>0.0007429843331851349</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>0.001073098309606926</v>
+        <v>0.0005707395684564604</v>
       </c>
       <c r="R139" t="n">
-        <v>0.001225024658478711</v>
+        <v>0.0007257598567122674</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -9275,10 +9275,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>0.001979760165425434</v>
+        <v>0.0006094831358585491</v>
       </c>
       <c r="R140" t="n">
-        <v>0.001300498209173383</v>
+        <v>0.0007141321846268956</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>0.001997785380982562</v>
+        <v>0.0006372444489717395</v>
       </c>
       <c r="R141" t="n">
-        <v>0.001370226926354301</v>
+        <v>0.00070644341106138</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>0.001196479023012001</v>
+        <v>0.0002279215093485616</v>
       </c>
       <c r="R142" t="n">
-        <v>0.001352852136020071</v>
+        <v>0.0006585912208900981</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -9464,10 +9464,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>0.001425976114613065</v>
+        <v>0.0002906504406916714</v>
       </c>
       <c r="R143" t="n">
-        <v>0.00136016453387937</v>
+        <v>0.0006217971428702554</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>0.001355966694015377</v>
+        <v>0.0001737881585557931</v>
       </c>
       <c r="R144" t="n">
-        <v>0.001359744749892971</v>
+        <v>0.0005769962444388092</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -9590,10 +9590,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>0.001663207972457002</v>
+        <v>0.0003757367527130866</v>
       </c>
       <c r="R145" t="n">
-        <v>0.001390091072149374</v>
+        <v>0.0005568702952662369</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -9653,10 +9653,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>0.0009794025354989302</v>
+        <v>0.0009836995479483137</v>
       </c>
       <c r="R146" t="n">
-        <v>0.001349022218484329</v>
+        <v>0.0005995532205344446</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -9716,10 +9716,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>0.001512418916647053</v>
+        <v>0.0005701100955718106</v>
       </c>
       <c r="R147" t="n">
-        <v>0.001365361888300602</v>
+        <v>0.0005966089080381812</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>0.02411072595895537</v>
+        <v>0.01174942144509436</v>
       </c>
       <c r="R148" t="n">
-        <v>0.00363989829536608</v>
+        <v>0.0017118901617438</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>0.001589068864227317</v>
+        <v>0.0002106581897797695</v>
       </c>
       <c r="R149" t="n">
-        <v>0.003434815352252203</v>
+        <v>0.001561766964547397</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>0.00151684915672648</v>
+        <v>0.0001753407710274174</v>
       </c>
       <c r="R150" t="n">
-        <v>0.003243018732699631</v>
+        <v>0.001423124345195399</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>0.002403459045842727</v>
+        <v>0.0009563382572797786</v>
       </c>
       <c r="R151" t="n">
-        <v>0.00315906276401394</v>
+        <v>0.001376445736403837</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>0.002598718844905326</v>
+        <v>0.0008541046652019964</v>
       </c>
       <c r="R152" t="n">
-        <v>0.003103028372103079</v>
+        <v>0.001324211629283652</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>0.002598718844905326</v>
+        <v>0.0008541046652019964</v>
       </c>
       <c r="R153" t="n">
-        <v>0.003052597419383303</v>
+        <v>0.001277200932875487</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -10157,10 +10157,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>0.0008197224602284519</v>
+        <v>0.0001134106716881373</v>
       </c>
       <c r="R154" t="n">
-        <v>0.002829309923467818</v>
+        <v>0.001160821906756752</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -10220,10 +10220,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>0.001229148558497335</v>
+        <v>0.0001412077587196053</v>
       </c>
       <c r="R155" t="n">
-        <v>0.002669293786970769</v>
+        <v>0.001058860491953037</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -10283,10 +10283,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>0.001229148558497335</v>
+        <v>0.0001412077587196053</v>
       </c>
       <c r="R156" t="n">
-        <v>0.002525279264123426</v>
+        <v>0.0009670952186296936</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>0.001559694393889174</v>
+        <v>0.0008475581056886976</v>
       </c>
       <c r="R157" t="n">
-        <v>0.002428720777100001</v>
+        <v>0.000955141507335594</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>0.003805527076391317</v>
+        <v>0.00207713435971698</v>
       </c>
       <c r="R158" t="n">
-        <v>0.002566401407029132</v>
+        <v>0.001067340792573733</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -10472,10 +10472,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>0.002719594598286013</v>
+        <v>0.001475830758119099</v>
       </c>
       <c r="R159" t="n">
-        <v>0.00258172072615482</v>
+        <v>0.001108189789128269</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -10535,10 +10535,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>0.0011211531247161</v>
+        <v>0.0007484176248694452</v>
       </c>
       <c r="R160" t="n">
-        <v>0.002435663966010948</v>
+        <v>0.001072212572702387</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>0.001211766204379419</v>
+        <v>0.0001249117544259878</v>
       </c>
       <c r="R161" t="n">
-        <v>0.002313274189847795</v>
+        <v>0.0009774824908747467</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -10661,10 +10661,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>0.001348085998934748</v>
+        <v>0.0001046148582888302</v>
       </c>
       <c r="R162" t="n">
-        <v>0.002216755370756491</v>
+        <v>0.000890195727616155</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -10724,10 +10724,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>0.001765692593266545</v>
+        <v>0.0007525749883057302</v>
       </c>
       <c r="R163" t="n">
-        <v>0.002171649093007496</v>
+        <v>0.0008764336536851125</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>0.002793596377840594</v>
+        <v>0.001398156521553311</v>
       </c>
       <c r="R164" t="n">
-        <v>0.002233843821490806</v>
+        <v>0.0009286059404719325</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -10850,10 +10850,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>0.002854452296021406</v>
+        <v>0.001309840764591273</v>
       </c>
       <c r="R165" t="n">
-        <v>0.002295904668943866</v>
+        <v>0.0009667294228838665</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>0.001762601792550337</v>
+        <v>0.000459005743270744</v>
       </c>
       <c r="R166" t="n">
-        <v>0.002242574381304513</v>
+        <v>0.0009159570549225543</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>0.001282742677135419</v>
+        <v>0.0002022611325113788</v>
       </c>
       <c r="R167" t="n">
-        <v>0.002146591210887604</v>
+        <v>0.0008445874626814366</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>0.001324972802587146</v>
+        <v>0.000181584481056698</v>
       </c>
       <c r="R168" t="n">
-        <v>0.002064429370057558</v>
+        <v>0.0007782871645189627</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>0.001492606150572098</v>
+        <v>0.0005308061265414953</v>
       </c>
       <c r="R169" t="n">
-        <v>0.002007247048109012</v>
+        <v>0.0007535390607212159</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -11165,10 +11165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>0.002129256239014409</v>
+        <v>0.0008998849534535219</v>
       </c>
       <c r="R170" t="n">
-        <v>0.002019447967199551</v>
+        <v>0.0007681736499944465</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -11228,10 +11228,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>0.00305081426003749</v>
+        <v>0.001275732585119962</v>
       </c>
       <c r="R171" t="n">
-        <v>0.002122584596483345</v>
+        <v>0.000818929543506998</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -11291,10 +11291,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>0.001066983289209595</v>
+        <v>0.001029218605860692</v>
       </c>
       <c r="R172" t="n">
-        <v>0.00201702446575597</v>
+        <v>0.0008399584497423674</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>0.001163408289890277</v>
+        <v>0.0006142507833321989</v>
       </c>
       <c r="R173" t="n">
-        <v>0.001931662848169401</v>
+        <v>0.0008173876831013506</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>0.001557147432199718</v>
+        <v>0.0003338969200844006</v>
       </c>
       <c r="R174" t="n">
-        <v>0.001894211306572433</v>
+        <v>0.0007690386067996555</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -11480,10 +11480,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>0.001483949634025213</v>
+        <v>0.0008421863370391069</v>
       </c>
       <c r="R175" t="n">
-        <v>0.001853185139317711</v>
+        <v>0.0007763533798236007</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>0.001714295974718121</v>
+        <v>0.0009274640512777121</v>
       </c>
       <c r="R176" t="n">
-        <v>0.001839296222857752</v>
+        <v>0.0007914644469690118</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -11606,10 +11606,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>0.001714295974718121</v>
+        <v>0.0009274640512777121</v>
       </c>
       <c r="R177" t="n">
-        <v>0.001826796198043789</v>
+        <v>0.0008050644073998817</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -11669,10 +11669,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>0.001313268875201991</v>
+        <v>0.001284529292878081</v>
       </c>
       <c r="R178" t="n">
-        <v>0.001775443465759609</v>
+        <v>0.0008530108959477016</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -11732,10 +11732,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>0.002158369362906028</v>
+        <v>0.0008587815557144302</v>
       </c>
       <c r="R179" t="n">
-        <v>0.001813736055474251</v>
+        <v>0.0008535879619243745</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
